--- a/data/trans_orig/Q5403-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2007</t>
+          <t>Población según si es capaz de ir de compras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50825</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>58855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69069</t>
+          <t>68486</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82283</t>
+          <t>82062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39469</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>49704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61804</t>
+          <t>61903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67445</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74141</t>
+          <t>73737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>88167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25104</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47701</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213609</t>
+          <t>212207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234589</t>
+          <t>234373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62552</t>
+          <t>62149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76823</t>
+          <t>76917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>280950</t>
+          <t>282869</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>306883</t>
+          <t>307983</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41907</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>51872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61655</t>
+          <t>61089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108301</t>
+          <t>108677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129822</t>
+          <t>129023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40799</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42282</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48601</t>
+          <t>50341</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78423</t>
+          <t>80146</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49822</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>79589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>315170</t>
+          <t>314609</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348722</t>
+          <t>348758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>319221</t>
+          <t>318351</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>353257</t>
+          <t>352950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60632</t>
+          <t>61022</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93885</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53273</t>
+          <t>53776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113600</t>
+          <t>114246</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157843</t>
+          <t>157016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>427478</t>
+          <t>425254</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>454564</t>
+          <t>454061</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>502123</t>
+          <t>503019</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>548181</t>
+          <t>548479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>941455</t>
+          <t>937341</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>992525</t>
+          <t>989772</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2012</t>
+          <t>Población según si es capaz de ir de compras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52909</t>
+          <t>53928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>66245</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>45878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57561</t>
+          <t>57451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>59005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73560</t>
+          <t>73459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107103</t>
+          <t>106760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>32255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45244</t>
+          <t>45831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127490</t>
+          <t>126967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150252</t>
+          <t>149793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41645</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54765</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160534</t>
+          <t>161484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187586</t>
+          <t>188230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>198238</t>
+          <t>200428</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230450</t>
+          <t>230301</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>44086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>58489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>48089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58660</t>
+          <t>59701</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87790</t>
+          <t>87218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>107872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133293</t>
+          <t>134487</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186053</t>
+          <t>185280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216536</t>
+          <t>216729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>46350</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77737</t>
+          <t>75323</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46951</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>76020</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60548</t>
+          <t>62054</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62905</t>
+          <t>61322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268271</t>
+          <t>268057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305680</t>
+          <t>304632</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>267295</t>
+          <t>272720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306409</t>
+          <t>307215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93478</t>
+          <t>93251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>135097</t>
+          <t>133387</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>139886</t>
+          <t>139247</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>188019</t>
+          <t>186876</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78486</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83461</t>
+          <t>85216</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>125010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>136115</t>
+          <t>138044</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>187255</t>
+          <t>190868</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>425811</t>
+          <t>429023</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>467905</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>501364</t>
+          <t>504137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>553848</t>
+          <t>551052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>944190</t>
+          <t>941041</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1008435</t>
+          <t>1007116</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2016</t>
+          <t>Población según si es capaz de ir de compras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57289</t>
+          <t>56240</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>66669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34582</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86008</t>
+          <t>86058</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100053</t>
+          <t>99208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54378</t>
+          <t>54232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65916</t>
+          <t>65621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102342</t>
+          <t>101542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114875</t>
+          <t>114564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134210</t>
+          <t>135855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152873</t>
+          <t>153450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>35089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164329</t>
+          <t>165175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183452</t>
+          <t>183247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66173</t>
+          <t>65309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84575</t>
+          <t>85066</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>236047</t>
+          <t>238753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>263820</t>
+          <t>264043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26003</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>17334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37821</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>57201</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105941</t>
+          <t>105995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124831</t>
+          <t>125033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106851</t>
+          <t>106329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129827</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219218</t>
+          <t>219703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249420</t>
+          <t>249643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58699</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53083</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86652</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53083</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86652</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281027</t>
+          <t>281527</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321481</t>
+          <t>322053</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281027</t>
+          <t>281527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321481</t>
+          <t>322053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>54460</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90698</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91033</t>
+          <t>89572</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>131373</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>101174</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>146616</t>
+          <t>144844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>139292</t>
+          <t>140756</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192244</t>
+          <t>192215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>494542</t>
+          <t>493153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>525021</t>
+          <t>525251</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>552605</t>
+          <t>552401</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>605425</t>
+          <t>604021</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1056701</t>
+          <t>1055363</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1120201</t>
+          <t>1118735</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2023</t>
+          <t>Población según si es capaz de ir de compras en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96509</t>
+          <t>96211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>103676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60398</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150896</t>
+          <t>151198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>162360</t>
+          <t>162618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76510</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87446</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41894</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114375</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126973</t>
+          <t>127778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82427</t>
+          <t>82507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92955</t>
+          <t>93027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118051</t>
+          <t>117843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132806</t>
+          <t>131969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63475</t>
+          <t>62569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>22775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38948</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71289</t>
+          <t>71371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172092</t>
+          <t>172328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193420</t>
+          <t>193058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>254696</t>
+          <t>253068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>320188</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>431982</t>
+          <t>433744</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>538058</t>
+          <t>537955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>46238</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55924</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44258</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62787</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>64984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77335</t>
+          <t>77061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115453</t>
+          <t>114665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133553</t>
+          <t>134007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>185773</t>
+          <t>184104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208128</t>
+          <t>206684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>73638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74061</t>
+          <t>75289</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54535</t>
+          <t>52871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74850</t>
+          <t>73151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53785</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74623</t>
+          <t>75622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>183732</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208154</t>
+          <t>208215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185355</t>
+          <t>182300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210052</t>
+          <t>208773</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>56018</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64484</t>
+          <t>68548</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164408</t>
+          <t>165569</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>115376</t>
+          <t>109592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>204416</t>
+          <t>203596</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75069</t>
+          <t>75197</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>71875</t>
+          <t>74673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>178753</t>
+          <t>177081</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>130325</t>
+          <t>129506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>237230</t>
+          <t>233517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>512471</t>
+          <t>511381</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>542220</t>
+          <t>542252</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>679676</t>
+          <t>681359</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>883481</t>
+          <t>875326</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1220224</t>
+          <t>1223754</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1400004</t>
+          <t>1421264</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5403-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58855</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68486</t>
+          <t>68563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>82053</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49704</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61903</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56281</t>
+          <t>56591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73737</t>
+          <t>74965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88167</t>
+          <t>88438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45788</t>
+          <t>46116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212207</t>
+          <t>213903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>234373</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>61771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76917</t>
+          <t>76506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282869</t>
+          <t>283237</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>307983</t>
+          <t>307700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>51582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61089</t>
+          <t>62439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79993</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108677</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129023</t>
+          <t>129965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41069</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50341</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80146</t>
+          <t>79335</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>78765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>314609</t>
+          <t>314570</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348758</t>
+          <t>348819</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318351</t>
+          <t>317113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>352950</t>
+          <t>353466</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70741</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61022</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>93991</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53776</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>78046</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114246</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157016</t>
+          <t>158909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>425254</t>
+          <t>426529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>454061</t>
+          <t>453217</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>503019</t>
+          <t>504644</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>548479</t>
+          <t>548216</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>937341</t>
+          <t>940659</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>989772</t>
+          <t>995473</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>53985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>66137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>57471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59005</t>
+          <t>58759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73459</t>
+          <t>73367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>88665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>107413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126967</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149793</t>
+          <t>150232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>47574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188230</t>
+          <t>187518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33655</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>48083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200428</t>
+          <t>199419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230301</t>
+          <t>230417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58489</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>33573</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70502</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107872</t>
+          <t>106399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134487</t>
+          <t>134568</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>185280</t>
+          <t>184763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216729</t>
+          <t>217004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>47101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75323</t>
+          <t>76097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46792</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76020</t>
+          <t>76167</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>62565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>60663</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268057</t>
+          <t>268789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>304632</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>272720</t>
+          <t>270310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307215</t>
+          <t>308293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>92112</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133387</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>139247</t>
+          <t>138553</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>186876</t>
+          <t>186606</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85216</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125010</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138044</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190868</t>
+          <t>188886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>429023</t>
+          <t>428171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>469295</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>504137</t>
+          <t>501445</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>551052</t>
+          <t>553010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>941041</t>
+          <t>943303</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1007116</t>
+          <t>1009187</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56240</t>
+          <t>57840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66669</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86058</t>
+          <t>86548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99208</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40360</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49868</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>54456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>66168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101542</t>
+          <t>102214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>114137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>41552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135855</t>
+          <t>135283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153450</t>
+          <t>152175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35089</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>20629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165175</t>
+          <t>164753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183247</t>
+          <t>183562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65309</t>
+          <t>65012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85066</t>
+          <t>84247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>238753</t>
+          <t>237862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>264043</t>
+          <t>264271</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>32575</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57201</t>
+          <t>58487</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105995</t>
+          <t>104946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125033</t>
+          <t>124736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106329</t>
+          <t>106569</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219703</t>
+          <t>220636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249643</t>
+          <t>250696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85988</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85988</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281527</t>
+          <t>279148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322053</t>
+          <t>320393</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281527</t>
+          <t>279148</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322053</t>
+          <t>320393</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54460</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90884</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89572</t>
+          <t>90149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>131693</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54753</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>101174</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>144844</t>
+          <t>144380</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>140756</t>
+          <t>139902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192215</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>493153</t>
+          <t>494789</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>525251</t>
+          <t>525322</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>552401</t>
+          <t>554533</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>604021</t>
+          <t>606725</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1055363</t>
+          <t>1058324</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1118735</t>
+          <t>1117200</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,22 +11041,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100824</t>
+          <t>113060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96211</t>
+          <t>108454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103676</t>
+          <t>116167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56780</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51300</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60583</t>
+          <t>69281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>157604</t>
+          <t>178288</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>151198</t>
+          <t>170915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>162618</t>
+          <t>183550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107005</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107005</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107005</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172326</t>
+          <t>194373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172326</t>
+          <t>194373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172326</t>
+          <t>194373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>84762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38514</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>121603</t>
+          <t>137065</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114161</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127778</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23117</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88425</t>
+          <t>98399</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82507</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93027</t>
+          <t>103188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32380</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>45286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>125685</t>
+          <t>138325</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117843</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131969</t>
+          <t>146011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154276</t>
+          <t>169854</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154276</t>
+          <t>169854</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154276</t>
+          <t>169854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>25696</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>34510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62569</t>
+          <t>51509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>32555</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71371</t>
+          <t>55175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>183025</t>
+          <t>201102</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172328</t>
+          <t>190068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193058</t>
+          <t>212011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>103501</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>253068</t>
+          <t>97006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320188</t>
+          <t>109823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>484353</t>
+          <t>304603</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>433744</t>
+          <t>290210</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>537955</t>
+          <t>316809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564285</t>
+          <t>390233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38478</t>
+          <t>41466</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>50471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>46687</t>
+          <t>49653</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38863</t>
+          <t>41087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55653</t>
+          <t>59706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>45601</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>58373</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>49380</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62860</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71688</t>
+          <t>78905</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64984</t>
+          <t>71738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77061</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>124546</t>
+          <t>133177</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114665</t>
+          <t>123459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134007</t>
+          <t>144052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>196233</t>
+          <t>212082</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184104</t>
+          <t>198735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206684</t>
+          <t>225055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>99864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296281</t>
+          <t>320108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>67278</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>55812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73638</t>
+          <t>79731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>63632</t>
+          <t>68966</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>54070</t>
+          <t>57948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75289</t>
+          <t>80625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>63684</t>
+          <t>68832</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>57792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73151</t>
+          <t>79843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64216</t>
+          <t>69348</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55098</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,27 +13547,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>195969</t>
+          <t>209672</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182329</t>
+          <t>195852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>208215</t>
+          <t>223812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>197028</t>
+          <t>210745</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182300</t>
+          <t>197416</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208773</t>
+          <t>223213</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>37381</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56018</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>126854</t>
+          <t>137636</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>121451</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>156135</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>171972</t>
+          <t>184599</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>166595</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>203596</t>
+          <t>205862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -13855,27 +13855,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>55153</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75197</t>
+          <t>82692</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>137290</t>
+          <t>150226</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74673</t>
+          <t>133682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>177081</t>
+          <t>167511</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>199495</t>
+          <t>218021</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129506</t>
+          <t>197270</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>233517</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>528111</t>
+          <t>584147</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>511381</t>
+          <t>567256</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>542252</t>
+          <t>599971</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>754395</t>
+          <t>596960</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>681359</t>
+          <t>576683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>875326</t>
+          <t>620700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1282506</t>
+          <t>1181108</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1223754</t>
+          <t>1154295</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1421264</t>
+          <t>1207018</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>635433</t>
+          <t>698906</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>635433</t>
+          <t>698906</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>635433</t>
+          <t>698906</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1653973</t>
+          <t>1583728</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1653973</t>
+          <t>1583728</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1653973</t>
+          <t>1583728</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
